--- a/GameConfig/Datas/_import_v1_preview/记忆配置表.xlsx
+++ b/GameConfig/Datas/_import_v1_preview/记忆配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="记忆配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="记忆配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -568,7 +568,11 @@
           <t>弹簧老化，快门卡死，已长时间无法使用了，不知道这里面还有多少小玩意还能工作呢，老周想。</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mem_camera_dead</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>E04</t>
@@ -592,7 +596,11 @@
           <t>相机镜头内部起雾，照片不清，老周说，这相机还能用的时候，平日里街坊都指着这台相机拍照。</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mem_camera_lens</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>E02</t>
@@ -616,7 +624,11 @@
           <t>镜架的螺丝拧得很紧，但能看出并不是新换的，陈先生的父亲说，这眼镜是结婚时配的了，跟了他四十年，换了镜架，就和换了个人一样。老周也问过为什么肯换镜腿却不肯换镜架，陈父没答。</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mem_glasses_frame</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>E04</t>
@@ -640,7 +652,11 @@
           <t>右镜腿换过，和左镜腿样式不一了，是陈父主动要求的，他觉得这副眼镜对他来说意义重大，能不更换任何部件便尽量不换。</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mem_glasses_temple</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>E06</t>
@@ -664,7 +680,11 @@
           <t>镜片蒙了灰，但稍加擦拭就会发现被保养得还是很好，老周说，陈父走之后的前几年，他还总是觉得他还活着，每每擦完眼镜却想起故人已逝，总有些莫名的怅然。</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mem_glasses_lens</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>E03</t>
@@ -736,7 +756,11 @@
           <t>钟上面雕了个小房间，里面的布谷鸟会准点出来报时</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>mem_clock_bird</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>E04</t>
